--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-09-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F442A3C9-26B6-4C3B-8421-E7034979E49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ACD2E0-38B5-4EE8-89BF-83765D13E2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32520" yWindow="855" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31755" yWindow="1695" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="258">
   <si>
     <t>SKU</t>
   </si>
@@ -788,6 +788,12 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£17.41</t>
+  </si>
+  <si>
+    <t>£20.38</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1326,7 @@
         <v>173</v>
       </c>
       <c r="Q3" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="R3" t="s">
         <v>187</v>
@@ -1376,7 +1382,7 @@
         <v>173</v>
       </c>
       <c r="Q4" t="s">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="R4" t="s">
         <v>188</v>
